--- a/data/gravel/State 6061 All-Road 2025.xlsx
+++ b/data/gravel/State 6061 All-Road 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10905"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{162BBB5D-D2B0-B041-9DB1-5DFD57F98B55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0013D997-5053-F143-9269-9C2127ABF7FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="29900" yWindow="-21180" windowWidth="25020" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="116">
   <si>
     <t>brand</t>
   </si>
@@ -378,6 +378,9 @@
   </si>
   <si>
     <t>a8:f33</t>
+  </si>
+  <si>
+    <t>https://www.statebicycle.com/cdn/shop/files/6061All-Road-GraniteGrey_650b_700c_-1.jpg?v=1698786039</t>
   </si>
 </sst>
 </file>
@@ -790,6 +793,9 @@
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B6" s="1" t="s">
+        <v>115</v>
+      </c>
       <c r="C6" s="3"/>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>

--- a/data/gravel/State 6061 All-Road 2025.xlsx
+++ b/data/gravel/State 6061 All-Road 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0013D997-5053-F143-9269-9C2127ABF7FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22B81716-A19D-414C-B294-2B4C62EA1385}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="29900" yWindow="-21180" windowWidth="25020" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="118">
   <si>
     <t>brand</t>
   </si>
@@ -381,6 +381,12 @@
   </si>
   <si>
     <t>https://www.statebicycle.com/cdn/shop/files/6061All-Road-GraniteGrey_650b_700c_-1.jpg?v=1698786039</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>Phoenix, Arizona, USA</t>
   </si>
 </sst>
 </file>
@@ -744,7 +750,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M73"/>
+  <dimension ref="A1:M74"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" style="1" customWidth="1"/>
@@ -1585,6 +1591,14 @@
         <v>79</v>
       </c>
     </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A74" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>117</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/data/gravel/State 6061 All-Road 2025.xlsx
+++ b/data/gravel/State 6061 All-Road 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11018"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22B81716-A19D-414C-B294-2B4C62EA1385}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4B54257-FF74-B440-A2C6-63244505DAEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/data/gravel/State 6061 All-Road 2025.xlsx
+++ b/data/gravel/State 6061 All-Road 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11018"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4B54257-FF74-B440-A2C6-63244505DAEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27FD0565-7317-9B4E-80D5-5944B9D28880}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="124">
   <si>
     <t>brand</t>
   </si>
@@ -387,6 +387,24 @@
   </si>
   <si>
     <t>Phoenix, Arizona, USA</t>
+  </si>
+  <si>
+    <t>head_tube_d</t>
+  </si>
+  <si>
+    <t>headset_upper</t>
+  </si>
+  <si>
+    <t>headset_lower</t>
+  </si>
+  <si>
+    <t>fork_steerer</t>
+  </si>
+  <si>
+    <t>fork_steerer_d</t>
+  </si>
+  <si>
+    <t>fork_material</t>
   </si>
 </sst>
 </file>
@@ -750,7 +768,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M74"/>
+  <dimension ref="A1:M80"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" style="1" customWidth="1"/>
@@ -1455,147 +1473,177 @@
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>81</v>
+        <v>118</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
-        <v>43</v>
+        <v>119</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B52" s="1">
-        <v>31.6</v>
+        <v>120</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
-        <v>45</v>
+        <v>121</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
-        <v>46</v>
+        <v>122</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
-        <v>47</v>
+        <v>123</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
-        <v>48</v>
+        <v>42</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
-        <v>50</v>
+        <v>44</v>
+      </c>
+      <c r="B58" s="1">
+        <v>31.6</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="B59" s="1" t="s">
-        <v>77</v>
+        <v>45</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" s="1" t="s">
-        <v>57</v>
+        <v>51</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="B70" s="1">
-        <v>679</v>
+        <v>56</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="B71" s="1">
-        <v>1399</v>
+        <v>57</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" s="1" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="B73" s="1" t="s">
-        <v>79</v>
+        <v>59</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A75" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A76" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B76" s="1">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A77" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B77" s="1">
+        <v>1399</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A78" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A79" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A80" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="B74" s="1" t="s">
+      <c r="B80" s="1" t="s">
         <v>117</v>
       </c>
     </row>

--- a/data/gravel/State 6061 All-Road 2025.xlsx
+++ b/data/gravel/State 6061 All-Road 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11116"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27FD0565-7317-9B4E-80D5-5944B9D28880}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F73B91C1-EB00-C54F-AE42-4A27B3FF5F56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="125">
   <si>
     <t>brand</t>
   </si>
@@ -405,6 +405,9 @@
   </si>
   <si>
     <t>fork_material</t>
+  </si>
+  <si>
+    <t>yes</t>
   </si>
 </sst>
 </file>
@@ -1599,6 +1602,9 @@
       <c r="A73" s="1" t="s">
         <v>59</v>
       </c>
+      <c r="B73" s="1" t="s">
+        <v>124</v>
+      </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74" s="1" t="s">
